--- a/selenium_automation/reports/Excel/Automation_Test_Report.xlsx
+++ b/selenium_automation/reports/Excel/Automation_Test_Report.xlsx
@@ -61,306 +61,309 @@
     <t>Verify login fails with invalid password</t>
   </si>
   <si>
+    <t>TC_WEB_AUTH_003</t>
+  </si>
+  <si>
+    <t>Verify login fails with unregistered email address</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_004</t>
+  </si>
+  <si>
+    <t>Verify password field masks input characters</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_005</t>
+  </si>
+  <si>
+    <t>Verify 'Remember Me' functionality persists session</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_006</t>
+  </si>
+  <si>
+    <t>Verify OTP generation on 2FA enabled account</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_007</t>
+  </si>
+  <si>
+    <t>Verify OTP verification with valid 6-digit code</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_008</t>
+  </si>
+  <si>
+    <t>Verify OTP verification fails on expired code</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_009</t>
+  </si>
+  <si>
+    <t>Verify account lockout after 5 consecutive failed attempts</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_010</t>
+  </si>
+  <si>
+    <t>Verify 'Forgot Password' link sends password reset email</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_011</t>
+  </si>
+  <si>
+    <t>Verify password reset token validation and expiration</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_012</t>
+  </si>
+  <si>
+    <t>Verify password reset with strong password policy</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_013</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth single sign-on redirect</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_014</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth token exchange and session creation</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_015</t>
+  </si>
+  <si>
+    <t>Verify user logout invalidates active auth token</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_016</t>
+  </si>
+  <si>
+    <t>Verify protected route redirection to login when unauthenticated</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_017</t>
+  </si>
+  <si>
+    <t>Verify SQL injection attempt in login email field is blocked</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_018</t>
+  </si>
+  <si>
+    <t>Verify XSS payload in login username field is sanitized</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_019</t>
+  </si>
+  <si>
+    <t>Verify session cookie has HttpOnly and Secure flags</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_020</t>
+  </si>
+  <si>
+    <t>Verify login page SSL/TLS certificate validity</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_021</t>
+  </si>
+  <si>
+    <t>Verify user login with valid email and password (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_022</t>
+  </si>
+  <si>
+    <t>Verify login fails with invalid password (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_023</t>
+  </si>
+  <si>
+    <t>Verify login fails with unregistered email address (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_024</t>
+  </si>
+  <si>
+    <t>Verify password field masks input characters (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_025</t>
+  </si>
+  <si>
+    <t>Verify 'Remember Me' functionality persists session (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_026</t>
+  </si>
+  <si>
+    <t>Verify OTP generation on 2FA enabled account (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_027</t>
+  </si>
+  <si>
+    <t>Verify OTP verification with valid 6-digit code (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_028</t>
+  </si>
+  <si>
+    <t>Verify OTP verification fails on expired code (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_029</t>
+  </si>
+  <si>
+    <t>Verify account lockout after 5 consecutive failed attempts (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_030</t>
+  </si>
+  <si>
+    <t>Verify 'Forgot Password' link sends password reset email (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_031</t>
+  </si>
+  <si>
+    <t>Verify password reset token validation and expiration (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_032</t>
+  </si>
+  <si>
+    <t>Verify password reset with strong password policy (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_033</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth single sign-on redirect (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_034</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth token exchange and session creation (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_035</t>
+  </si>
+  <si>
+    <t>Verify user logout invalidates active auth token (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_036</t>
+  </si>
+  <si>
+    <t>Verify protected route redirection to login when unauthenticated (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_037</t>
+  </si>
+  <si>
+    <t>Verify SQL injection attempt in login email field is blocked (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_038</t>
+  </si>
+  <si>
+    <t>Verify XSS payload in login username field is sanitized (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_039</t>
+  </si>
+  <si>
+    <t>Verify session cookie has HttpOnly and Secure flags (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTH_040</t>
+  </si>
+  <si>
+    <t>Verify login page SSL/TLS certificate validity (Variation 2 - Boundary &amp; Edge Case)</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_001</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>Verify admin user access to Admin Panel dashboard</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_002</t>
+  </si>
+  <si>
+    <t>Verify regular donor is denied access to /admin route</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_003</t>
+  </si>
+  <si>
+    <t>Verify hospital staff can access blood inventory update view</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_004</t>
+  </si>
+  <si>
+    <t>Verify recipient cannot edit blood camp schedules without organizer role</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_005</t>
+  </si>
+  <si>
+    <t>Verify super-admin role can manage hospital credentials</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_006</t>
+  </si>
+  <si>
+    <t>Verify JWT role claim tampering is rejected with 403 Forbidden</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_007</t>
+  </si>
+  <si>
+    <t>Verify IDOR prevention when donor accesses another donor's private profile</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_008</t>
+  </si>
+  <si>
+    <t>Verify blood request approval restricted to authorized medical officers</t>
+  </si>
+  <si>
+    <t>TC_WEB_AUTHZ_009</t>
+  </si>
+  <si>
+    <t>Verify donor cannot view private medical notes of other donors</t>
+  </si>
+  <si>
     <t>0.01</t>
   </si>
   <si>
-    <t>TC_WEB_AUTH_003</t>
-  </si>
-  <si>
-    <t>Verify login fails with unregistered email address</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_004</t>
-  </si>
-  <si>
-    <t>Verify password field masks input characters</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_005</t>
-  </si>
-  <si>
-    <t>Verify 'Remember Me' functionality persists session</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_006</t>
-  </si>
-  <si>
-    <t>Verify OTP generation on 2FA enabled account</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_007</t>
-  </si>
-  <si>
-    <t>Verify OTP verification with valid 6-digit code</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_008</t>
-  </si>
-  <si>
-    <t>Verify OTP verification fails on expired code</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_009</t>
-  </si>
-  <si>
-    <t>Verify account lockout after 5 consecutive failed attempts</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_010</t>
-  </si>
-  <si>
-    <t>Verify 'Forgot Password' link sends password reset email</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_011</t>
-  </si>
-  <si>
-    <t>Verify password reset token validation and expiration</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_012</t>
-  </si>
-  <si>
-    <t>Verify password reset with strong password policy</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_013</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth single sign-on redirect</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_014</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth token exchange and session creation</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_015</t>
-  </si>
-  <si>
-    <t>Verify user logout invalidates active auth token</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_016</t>
-  </si>
-  <si>
-    <t>Verify protected route redirection to login when unauthenticated</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_017</t>
-  </si>
-  <si>
-    <t>Verify SQL injection attempt in login email field is blocked</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_018</t>
-  </si>
-  <si>
-    <t>Verify XSS payload in login username field is sanitized</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_019</t>
-  </si>
-  <si>
-    <t>Verify session cookie has HttpOnly and Secure flags</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_020</t>
-  </si>
-  <si>
-    <t>Verify login page SSL/TLS certificate validity</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_021</t>
-  </si>
-  <si>
-    <t>Verify user login with valid email and password (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_022</t>
-  </si>
-  <si>
-    <t>Verify login fails with invalid password (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_023</t>
-  </si>
-  <si>
-    <t>Verify login fails with unregistered email address (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_024</t>
-  </si>
-  <si>
-    <t>Verify password field masks input characters (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_025</t>
-  </si>
-  <si>
-    <t>Verify 'Remember Me' functionality persists session (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_026</t>
-  </si>
-  <si>
-    <t>Verify OTP generation on 2FA enabled account (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_027</t>
-  </si>
-  <si>
-    <t>Verify OTP verification with valid 6-digit code (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_028</t>
-  </si>
-  <si>
-    <t>Verify OTP verification fails on expired code (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_029</t>
-  </si>
-  <si>
-    <t>Verify account lockout after 5 consecutive failed attempts (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_030</t>
-  </si>
-  <si>
-    <t>Verify 'Forgot Password' link sends password reset email (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_031</t>
-  </si>
-  <si>
-    <t>Verify password reset token validation and expiration (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_032</t>
-  </si>
-  <si>
-    <t>Verify password reset with strong password policy (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_033</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth single sign-on redirect (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_034</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth token exchange and session creation (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_035</t>
-  </si>
-  <si>
-    <t>Verify user logout invalidates active auth token (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_036</t>
-  </si>
-  <si>
-    <t>Verify protected route redirection to login when unauthenticated (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_037</t>
-  </si>
-  <si>
-    <t>Verify SQL injection attempt in login email field is blocked (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_038</t>
-  </si>
-  <si>
-    <t>Verify XSS payload in login username field is sanitized (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_039</t>
-  </si>
-  <si>
-    <t>Verify session cookie has HttpOnly and Secure flags (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTH_040</t>
-  </si>
-  <si>
-    <t>Verify login page SSL/TLS certificate validity (Variation 2 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_001</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Verify admin user access to Admin Panel dashboard</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_002</t>
-  </si>
-  <si>
-    <t>Verify regular donor is denied access to /admin route</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_003</t>
-  </si>
-  <si>
-    <t>Verify hospital staff can access blood inventory update view</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_004</t>
-  </si>
-  <si>
-    <t>Verify recipient cannot edit blood camp schedules without organizer role</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_005</t>
-  </si>
-  <si>
-    <t>Verify super-admin role can manage hospital credentials</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_006</t>
-  </si>
-  <si>
-    <t>Verify JWT role claim tampering is rejected with 403 Forbidden</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_007</t>
-  </si>
-  <si>
-    <t>Verify IDOR prevention when donor accesses another donor's private profile</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_008</t>
-  </si>
-  <si>
-    <t>Verify blood request approval restricted to authorized medical officers</t>
-  </si>
-  <si>
-    <t>TC_WEB_AUTHZ_009</t>
-  </si>
-  <si>
-    <t>Verify donor cannot view private medical notes of other donors</t>
-  </si>
-  <si>
     <t>TC_WEB_AUTHZ_010</t>
   </si>
   <si>
@@ -473,9 +476,6 @@
   </si>
   <si>
     <t>Verify blood request approval restricted to authorized medical officers (Variation 3 - Boundary &amp; Edge Case)</t>
-  </si>
-  <si>
-    <t>0.05</t>
   </si>
   <si>
     <t>TC_WEB_AUTHZ_029</t>
@@ -4035,27 +4035,27 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,18 +4095,18 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>9</v>
@@ -4120,33 +4120,33 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -4160,13 +4160,13 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -4175,18 +4175,18 @@
         <v>10</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
@@ -4195,21 +4195,21 @@
         <v>10</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>10</v>
@@ -4220,13 +4220,13 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>20</v>
@@ -4235,18 +4235,18 @@
         <v>10</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
@@ -4255,18 +4255,18 @@
         <v>10</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>9</v>
@@ -4275,38 +4275,38 @@
         <v>10</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>20</v>
@@ -4315,18 +4315,18 @@
         <v>10</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>9</v>
@@ -4335,18 +4335,18 @@
         <v>10</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>9</v>
@@ -4355,21 +4355,21 @@
         <v>10</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>10</v>
@@ -4380,13 +4380,13 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>20</v>
@@ -4395,18 +4395,18 @@
         <v>10</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>9</v>
@@ -4415,18 +4415,18 @@
         <v>10</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>9</v>
@@ -4435,38 +4435,38 @@
         <v>10</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>20</v>
@@ -4475,18 +4475,18 @@
         <v>10</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>9</v>
@@ -4495,18 +4495,18 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>9</v>
@@ -4515,27 +4515,27 @@
         <v>10</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4555,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4575,7 +4575,7 @@
         <v>10</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4595,7 +4595,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4609,13 +4609,13 @@
         <v>76</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4635,7 +4635,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4655,7 +4655,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4675,7 +4675,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4689,7 +4689,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>10</v>
@@ -4715,7 +4715,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4735,7 +4735,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4755,7 +4755,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4769,13 +4769,13 @@
         <v>92</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4795,7 +4795,7 @@
         <v>10</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,7 +4815,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4849,13 +4849,13 @@
         <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4869,13 +4869,13 @@
         <v>103</v>
       </c>
       <c r="D45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4895,7 +4895,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4915,7 +4915,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4929,13 +4929,13 @@
         <v>109</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4949,13 +4949,13 @@
         <v>111</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,18 +4975,18 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>9</v>
@@ -5000,16 +5000,16 @@
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>10</v>
@@ -5020,33 +5020,33 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>9</v>
@@ -5055,18 +5055,18 @@
         <v>10</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>9</v>
@@ -5075,21 +5075,21 @@
         <v>10</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>10</v>
@@ -5100,33 +5100,33 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>9</v>
@@ -5135,18 +5135,18 @@
         <v>10</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>9</v>
@@ -5155,58 +5155,58 @@
         <v>10</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>9</v>
@@ -5215,18 +5215,18 @@
         <v>10</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>9</v>
@@ -5235,58 +5235,58 @@
         <v>10</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>9</v>
@@ -5295,18 +5295,18 @@
         <v>10</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>9</v>
@@ -5315,47 +5315,47 @@
         <v>10</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5409,13 +5409,13 @@
         <v>158</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5429,13 +5429,13 @@
         <v>160</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5455,7 +5455,7 @@
         <v>10</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5475,7 +5475,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5489,13 +5489,13 @@
         <v>166</v>
       </c>
       <c r="D76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5509,13 +5509,13 @@
         <v>168</v>
       </c>
       <c r="D77" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5535,7 +5535,7 @@
         <v>10</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5569,13 +5569,13 @@
         <v>174</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5589,13 +5589,13 @@
         <v>176</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5609,13 +5609,13 @@
         <v>179</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5629,13 +5629,13 @@
         <v>181</v>
       </c>
       <c r="D83" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5655,7 +5655,7 @@
         <v>10</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5675,7 +5675,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5689,7 +5689,7 @@
         <v>187</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>10</v>
@@ -5709,13 +5709,13 @@
         <v>189</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,7 +5755,7 @@
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5769,13 +5769,13 @@
         <v>195</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5789,13 +5789,13 @@
         <v>197</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5835,7 +5835,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5849,13 +5849,13 @@
         <v>203</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5869,13 +5869,13 @@
         <v>205</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5895,7 +5895,7 @@
         <v>10</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5915,7 +5915,7 @@
         <v>10</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5929,13 +5929,13 @@
         <v>211</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5949,13 +5949,13 @@
         <v>213</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5975,7 +5975,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5995,7 +5995,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6009,13 +6009,13 @@
         <v>219</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6029,13 +6029,13 @@
         <v>221</v>
       </c>
       <c r="D103" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6055,7 +6055,7 @@
         <v>10</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6089,13 +6089,13 @@
         <v>227</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6109,13 +6109,13 @@
         <v>229</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6135,7 +6135,7 @@
         <v>10</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6155,7 +6155,7 @@
         <v>10</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6169,13 +6169,13 @@
         <v>235</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6189,7 +6189,7 @@
         <v>237</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>10</v>
@@ -6209,13 +6209,13 @@
         <v>240</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6235,7 +6235,7 @@
         <v>10</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6249,13 +6249,13 @@
         <v>244</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6275,7 +6275,7 @@
         <v>10</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6289,13 +6289,13 @@
         <v>248</v>
       </c>
       <c r="D116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6329,13 +6329,13 @@
         <v>252</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6355,7 +6355,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6369,13 +6369,13 @@
         <v>256</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6409,13 +6409,13 @@
         <v>260</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6435,7 +6435,7 @@
         <v>10</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6449,13 +6449,13 @@
         <v>264</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6475,7 +6475,7 @@
         <v>10</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6489,7 +6489,7 @@
         <v>268</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>10</v>
@@ -6515,7 +6515,7 @@
         <v>10</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6529,7 +6529,7 @@
         <v>272</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>10</v>
@@ -6555,7 +6555,7 @@
         <v>10</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6569,7 +6569,7 @@
         <v>276</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>10</v>
@@ -6595,7 +6595,7 @@
         <v>10</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6609,13 +6609,13 @@
         <v>280</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6635,7 +6635,7 @@
         <v>10</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6649,7 +6649,7 @@
         <v>284</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>10</v>
@@ -6675,7 +6675,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6689,7 +6689,7 @@
         <v>288</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>10</v>
@@ -6715,7 +6715,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6729,13 +6729,13 @@
         <v>292</v>
       </c>
       <c r="D138" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="139" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6755,7 +6755,7 @@
         <v>10</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6769,7 +6769,7 @@
         <v>296</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>10</v>
@@ -6795,7 +6795,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="142" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6809,13 +6809,13 @@
         <v>300</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6835,7 +6835,7 @@
         <v>10</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="144" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6849,13 +6849,13 @@
         <v>304</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6889,13 +6889,13 @@
         <v>308</v>
       </c>
       <c r="D146" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="147" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6915,7 +6915,7 @@
         <v>10</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6929,13 +6929,13 @@
         <v>312</v>
       </c>
       <c r="D148" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F148" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="149" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6955,7 +6955,7 @@
         <v>10</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6969,13 +6969,13 @@
         <v>316</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6995,7 +6995,7 @@
         <v>10</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7009,13 +7009,13 @@
         <v>320</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="153" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7049,13 +7049,13 @@
         <v>324</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="155" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7075,7 +7075,7 @@
         <v>10</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7089,13 +7089,13 @@
         <v>328</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7129,13 +7129,13 @@
         <v>332</v>
       </c>
       <c r="D158" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="159" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7155,7 +7155,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7169,13 +7169,13 @@
         <v>336</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="161" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7195,7 +7195,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="162" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7215,7 +7215,7 @@
         <v>10</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7229,13 +7229,13 @@
         <v>343</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7249,13 +7249,13 @@
         <v>345</v>
       </c>
       <c r="D164" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="165" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7295,7 +7295,7 @@
         <v>10</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7309,13 +7309,13 @@
         <v>351</v>
       </c>
       <c r="D167" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F167" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F167" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="168" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7329,13 +7329,13 @@
         <v>353</v>
       </c>
       <c r="D168" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="169" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7355,7 +7355,7 @@
         <v>10</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7375,7 +7375,7 @@
         <v>10</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7389,13 +7389,13 @@
         <v>359</v>
       </c>
       <c r="D171" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F171" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F171" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="172" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7409,13 +7409,13 @@
         <v>361</v>
       </c>
       <c r="D172" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F172" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F172" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="173" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7435,7 +7435,7 @@
         <v>10</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7455,7 +7455,7 @@
         <v>10</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="175" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7469,13 +7469,13 @@
         <v>367</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7489,13 +7489,13 @@
         <v>369</v>
       </c>
       <c r="D176" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E176" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="177" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7535,7 +7535,7 @@
         <v>10</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7549,13 +7549,13 @@
         <v>375</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7569,13 +7569,13 @@
         <v>377</v>
       </c>
       <c r="D180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="181" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7595,7 +7595,7 @@
         <v>10</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7615,7 +7615,7 @@
         <v>10</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="183" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7629,13 +7629,13 @@
         <v>383</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7649,13 +7649,13 @@
         <v>385</v>
       </c>
       <c r="D184" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="185" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7695,7 +7695,7 @@
         <v>10</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7709,13 +7709,13 @@
         <v>391</v>
       </c>
       <c r="D187" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F187" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F187" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="188" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7729,13 +7729,13 @@
         <v>393</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="189" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7755,7 +7755,7 @@
         <v>10</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7789,13 +7789,13 @@
         <v>399</v>
       </c>
       <c r="D191" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F191" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="192" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7809,13 +7809,13 @@
         <v>401</v>
       </c>
       <c r="D192" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F192" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="193" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7835,7 +7835,7 @@
         <v>10</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7869,13 +7869,13 @@
         <v>407</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7889,13 +7889,13 @@
         <v>409</v>
       </c>
       <c r="D196" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="197" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7915,7 +7915,7 @@
         <v>10</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="198" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7949,13 +7949,13 @@
         <v>415</v>
       </c>
       <c r="D199" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F199" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E199" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F199" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="200" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7969,13 +7969,13 @@
         <v>417</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="201" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7995,7 +7995,7 @@
         <v>10</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8015,7 +8015,7 @@
         <v>10</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8029,13 +8029,13 @@
         <v>423</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="204" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8049,7 +8049,7 @@
         <v>425</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>10</v>
@@ -8095,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8109,13 +8109,13 @@
         <v>431</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8129,13 +8129,13 @@
         <v>433</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="209" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8155,7 +8155,7 @@
         <v>10</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="210" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8175,7 +8175,7 @@
         <v>10</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="211" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8189,13 +8189,13 @@
         <v>439</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8215,7 +8215,7 @@
         <v>10</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="213" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8235,7 +8235,7 @@
         <v>10</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="214" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8249,13 +8249,13 @@
         <v>446</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="215" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8269,13 +8269,13 @@
         <v>448</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8295,7 +8295,7 @@
         <v>10</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="217" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8315,7 +8315,7 @@
         <v>10</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8329,13 +8329,13 @@
         <v>454</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="219" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8349,13 +8349,13 @@
         <v>456</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="220" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8375,7 +8375,7 @@
         <v>10</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="221" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8395,7 +8395,7 @@
         <v>10</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="222" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8409,13 +8409,13 @@
         <v>462</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8429,13 +8429,13 @@
         <v>464</v>
       </c>
       <c r="D223" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F223" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E223" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F223" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="224" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8455,7 +8455,7 @@
         <v>10</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="225" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8475,7 +8475,7 @@
         <v>10</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8489,13 +8489,13 @@
         <v>470</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8509,13 +8509,13 @@
         <v>472</v>
       </c>
       <c r="D227" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F227" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F227" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="228" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8535,7 +8535,7 @@
         <v>10</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="229" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8555,7 +8555,7 @@
         <v>10</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="230" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8569,13 +8569,13 @@
         <v>478</v>
       </c>
       <c r="D230" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="231" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8589,13 +8589,13 @@
         <v>480</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="232" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8635,7 +8635,7 @@
         <v>10</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="234" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8649,13 +8649,13 @@
         <v>486</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="235" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8669,13 +8669,13 @@
         <v>488</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="236" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8695,7 +8695,7 @@
         <v>10</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8729,13 +8729,13 @@
         <v>494</v>
       </c>
       <c r="D238" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E238" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="239" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8749,13 +8749,13 @@
         <v>496</v>
       </c>
       <c r="D239" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F239" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E239" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F239" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="240" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8775,7 +8775,7 @@
         <v>10</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="241" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8795,7 +8795,7 @@
         <v>10</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="242" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8809,7 +8809,7 @@
         <v>502</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>10</v>
@@ -8829,13 +8829,13 @@
         <v>504</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="244" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8875,7 +8875,7 @@
         <v>10</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="246" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8889,13 +8889,13 @@
         <v>510</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="247" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8909,13 +8909,13 @@
         <v>512</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="248" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8935,7 +8935,7 @@
         <v>10</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="249" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8955,7 +8955,7 @@
         <v>10</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="250" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8969,13 +8969,13 @@
         <v>518</v>
       </c>
       <c r="D250" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="251" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8989,7 +8989,7 @@
         <v>520</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>10</v>
@@ -9015,7 +9015,7 @@
         <v>10</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="253" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9035,7 +9035,7 @@
         <v>10</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="254" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9049,13 +9049,13 @@
         <v>526</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9069,13 +9069,13 @@
         <v>528</v>
       </c>
       <c r="D255" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F255" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F255" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="256" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9095,7 +9095,7 @@
         <v>10</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="257" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9115,7 +9115,7 @@
         <v>10</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="258" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9129,13 +9129,13 @@
         <v>534</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="259" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9149,13 +9149,13 @@
         <v>536</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="260" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9175,7 +9175,7 @@
         <v>10</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="261" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9195,7 +9195,7 @@
         <v>10</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="262" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9215,7 +9215,7 @@
         <v>10</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="263" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9229,13 +9229,13 @@
         <v>545</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="264" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9249,13 +9249,13 @@
         <v>547</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="265" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9275,7 +9275,7 @@
         <v>10</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="266" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9309,7 +9309,7 @@
         <v>553</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>10</v>
@@ -9329,13 +9329,13 @@
         <v>555</v>
       </c>
       <c r="D268" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F268" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E268" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="269" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9355,7 +9355,7 @@
         <v>10</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="270" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="271" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9389,13 +9389,13 @@
         <v>561</v>
       </c>
       <c r="D271" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F271" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E271" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F271" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="272" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9409,13 +9409,13 @@
         <v>563</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="273" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9435,7 +9435,7 @@
         <v>10</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="274" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9455,7 +9455,7 @@
         <v>10</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="275" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9469,7 +9469,7 @@
         <v>569</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>10</v>
@@ -9489,13 +9489,13 @@
         <v>571</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="277" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9515,7 +9515,7 @@
         <v>10</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="278" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9535,7 +9535,7 @@
         <v>10</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="279" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9549,13 +9549,13 @@
         <v>577</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="280" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9569,13 +9569,13 @@
         <v>579</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="281" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9595,7 +9595,7 @@
         <v>10</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="282" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9629,13 +9629,13 @@
         <v>585</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="284" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9649,13 +9649,13 @@
         <v>587</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E284" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="285" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9675,7 +9675,7 @@
         <v>10</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="286" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9709,13 +9709,13 @@
         <v>593</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E287" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="288" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9729,13 +9729,13 @@
         <v>595</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E288" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="289" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9755,7 +9755,7 @@
         <v>10</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="290" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9775,7 +9775,7 @@
         <v>10</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="291" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9789,13 +9789,13 @@
         <v>601</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="292" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9809,7 +9809,7 @@
         <v>603</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E292" s="3" t="s">
         <v>10</v>
@@ -9835,7 +9835,7 @@
         <v>10</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="294" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9855,7 +9855,7 @@
         <v>10</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="295" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9869,7 +9869,7 @@
         <v>609</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>10</v>
@@ -9889,13 +9889,13 @@
         <v>611</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="297" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9915,7 +9915,7 @@
         <v>10</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="298" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9935,7 +9935,7 @@
         <v>10</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="299" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9949,13 +9949,13 @@
         <v>617</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E299" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="300" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9969,7 +9969,7 @@
         <v>619</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E300" s="3" t="s">
         <v>10</v>
@@ -10009,13 +10009,13 @@
         <v>624</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F302" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E302" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="303" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10029,13 +10029,13 @@
         <v>626</v>
       </c>
       <c r="D303" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F303" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E303" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F303" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="304" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10055,7 +10055,7 @@
         <v>10</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="305" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10075,7 +10075,7 @@
         <v>10</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="306" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10089,13 +10089,13 @@
         <v>632</v>
       </c>
       <c r="D306" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F306" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E306" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="307" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10109,13 +10109,13 @@
         <v>634</v>
       </c>
       <c r="D307" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F307" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E307" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F307" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="308" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10135,7 +10135,7 @@
         <v>10</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="309" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10155,7 +10155,7 @@
         <v>10</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="310" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10169,7 +10169,7 @@
         <v>640</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E310" s="3" t="s">
         <v>10</v>
@@ -10189,13 +10189,13 @@
         <v>642</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="312" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10215,7 +10215,7 @@
         <v>10</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="313" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10235,7 +10235,7 @@
         <v>10</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10249,13 +10249,13 @@
         <v>648</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E314" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="315" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10269,13 +10269,13 @@
         <v>650</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="316" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10295,7 +10295,7 @@
         <v>10</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="317" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10315,7 +10315,7 @@
         <v>10</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="318" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10329,13 +10329,13 @@
         <v>656</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="319" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10349,13 +10349,13 @@
         <v>658</v>
       </c>
       <c r="D319" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F319" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E319" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F319" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="320" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10395,7 +10395,7 @@
         <v>10</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="322" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10415,7 +10415,7 @@
         <v>10</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="323" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10435,7 +10435,7 @@
         <v>10</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="324" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10449,13 +10449,13 @@
         <v>669</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="325" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10469,13 +10469,13 @@
         <v>671</v>
       </c>
       <c r="D325" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F325" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E325" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F325" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="326" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10495,7 +10495,7 @@
         <v>10</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="327" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10515,7 +10515,7 @@
         <v>10</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="328" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10529,13 +10529,13 @@
         <v>677</v>
       </c>
       <c r="D328" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E328" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F328" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E328" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F328" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="329" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10549,7 +10549,7 @@
         <v>679</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>10</v>
@@ -10575,7 +10575,7 @@
         <v>10</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="331" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10609,13 +10609,13 @@
         <v>685</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E332" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="333" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10629,13 +10629,13 @@
         <v>687</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E333" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="334" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10655,7 +10655,7 @@
         <v>10</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="335" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10675,7 +10675,7 @@
         <v>10</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="336" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10689,13 +10689,13 @@
         <v>693</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="337" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10709,13 +10709,13 @@
         <v>695</v>
       </c>
       <c r="D337" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E337" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F337" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E337" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F337" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="338" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10735,7 +10735,7 @@
         <v>10</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="339" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10755,7 +10755,7 @@
         <v>10</v>
       </c>
       <c r="F339" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="340" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10769,13 +10769,13 @@
         <v>701</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="341" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10789,13 +10789,13 @@
         <v>703</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F341" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="342" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10809,13 +10809,13 @@
         <v>706</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E342" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="343" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10829,13 +10829,13 @@
         <v>708</v>
       </c>
       <c r="D343" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E343" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F343" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E343" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F343" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="344" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10855,7 +10855,7 @@
         <v>10</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="345" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10875,7 +10875,7 @@
         <v>10</v>
       </c>
       <c r="F345" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="346" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10889,13 +10889,13 @@
         <v>714</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="347" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10909,13 +10909,13 @@
         <v>716</v>
       </c>
       <c r="D347" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E347" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F347" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E347" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F347" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="348" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10935,7 +10935,7 @@
         <v>10</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="349" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10955,7 +10955,7 @@
         <v>10</v>
       </c>
       <c r="F349" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="350" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10969,13 +10969,13 @@
         <v>722</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="351" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10989,13 +10989,13 @@
         <v>724</v>
       </c>
       <c r="D351" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E351" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F351" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E351" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F351" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="352" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11015,7 +11015,7 @@
         <v>10</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="353" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11035,7 +11035,7 @@
         <v>10</v>
       </c>
       <c r="F353" s="4" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="354" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11049,13 +11049,13 @@
         <v>730</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="355" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11069,13 +11069,13 @@
         <v>732</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F355" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="356" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11095,7 +11095,7 @@
         <v>10</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="357" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11115,7 +11115,7 @@
         <v>10</v>
       </c>
       <c r="F357" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="358" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11129,13 +11129,13 @@
         <v>738</v>
       </c>
       <c r="D358" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F358" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E358" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F358" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="359" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11149,13 +11149,13 @@
         <v>740</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F359" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="360" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11175,7 +11175,7 @@
         <v>10</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="361" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11195,7 +11195,7 @@
         <v>10</v>
       </c>
       <c r="F361" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="362" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11229,13 +11229,13 @@
         <v>749</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F363" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="364" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11255,7 +11255,7 @@
         <v>10</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="365" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11269,13 +11269,13 @@
         <v>753</v>
       </c>
       <c r="D365" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E365" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F365" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E365" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F365" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="366" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11295,7 +11295,7 @@
         <v>10</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="367" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11309,13 +11309,13 @@
         <v>757</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F367" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="368" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11335,7 +11335,7 @@
         <v>10</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="369" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11349,7 +11349,7 @@
         <v>761</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>10</v>
@@ -11375,7 +11375,7 @@
         <v>10</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="371" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11389,13 +11389,13 @@
         <v>765</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F371" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="372" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11415,7 +11415,7 @@
         <v>10</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="373" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11429,13 +11429,13 @@
         <v>769</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F373" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="374" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11455,7 +11455,7 @@
         <v>10</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="375" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11469,7 +11469,7 @@
         <v>773</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>10</v>
@@ -11495,7 +11495,7 @@
         <v>10</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
     </row>
     <row r="377" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11509,7 +11509,7 @@
         <v>777</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>10</v>
@@ -11535,7 +11535,7 @@
         <v>10</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="379" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11549,13 +11549,13 @@
         <v>781</v>
       </c>
       <c r="D379" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E379" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F379" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E379" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F379" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="380" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11589,13 +11589,13 @@
         <v>785</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E381" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F381" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="382" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11609,7 +11609,7 @@
         <v>788</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>10</v>
@@ -11635,7 +11635,7 @@
         <v>10</v>
       </c>
       <c r="F383" s="4" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="384" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11649,13 +11649,13 @@
         <v>792</v>
       </c>
       <c r="D384" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E384" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F384" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E384" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F384" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="385" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11675,7 +11675,7 @@
         <v>10</v>
       </c>
       <c r="F385" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="386" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11689,13 +11689,13 @@
         <v>796</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="387" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11715,7 +11715,7 @@
         <v>10</v>
       </c>
       <c r="F387" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="388" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11729,13 +11729,13 @@
         <v>800</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="389" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11769,13 +11769,13 @@
         <v>804</v>
       </c>
       <c r="D390" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E390" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F390" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E390" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F390" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11795,7 +11795,7 @@
         <v>10</v>
       </c>
       <c r="F391" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11809,13 +11809,13 @@
         <v>808</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E392" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11835,7 +11835,7 @@
         <v>10</v>
       </c>
       <c r="F393" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="394" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11849,13 +11849,13 @@
         <v>812</v>
       </c>
       <c r="D394" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E394" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F394" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E394" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F394" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="395" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11875,7 +11875,7 @@
         <v>10</v>
       </c>
       <c r="F395" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="396" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11889,13 +11889,13 @@
         <v>816</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E396" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="397" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11915,7 +11915,7 @@
         <v>10</v>
       </c>
       <c r="F397" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="398" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11929,13 +11929,13 @@
         <v>820</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="399" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11955,7 +11955,7 @@
         <v>10</v>
       </c>
       <c r="F399" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="400" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11969,13 +11969,13 @@
         <v>824</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E400" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="401" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11995,7 +11995,7 @@
         <v>10</v>
       </c>
       <c r="F401" s="4" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="402" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12009,13 +12009,13 @@
         <v>829</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E402" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12049,13 +12049,13 @@
         <v>833</v>
       </c>
       <c r="D404" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E404" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F404" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E404" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F404" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="405" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12075,7 +12075,7 @@
         <v>10</v>
       </c>
       <c r="F405" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="406" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12089,13 +12089,13 @@
         <v>837</v>
       </c>
       <c r="D406" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E406" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F406" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E406" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F406" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="407" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12115,7 +12115,7 @@
         <v>10</v>
       </c>
       <c r="F407" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="408" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12129,13 +12129,13 @@
         <v>841</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E408" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12155,7 +12155,7 @@
         <v>10</v>
       </c>
       <c r="F409" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="410" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12169,13 +12169,13 @@
         <v>845</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E410" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="411" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12195,7 +12195,7 @@
         <v>10</v>
       </c>
       <c r="F411" s="4" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="412" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12209,13 +12209,13 @@
         <v>849</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="413" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12235,7 +12235,7 @@
         <v>10</v>
       </c>
       <c r="F413" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="414" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12249,13 +12249,13 @@
         <v>853</v>
       </c>
       <c r="D414" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E414" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F414" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E414" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F414" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="415" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12275,7 +12275,7 @@
         <v>10</v>
       </c>
       <c r="F415" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="416" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12289,7 +12289,7 @@
         <v>857</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E416" s="3" t="s">
         <v>10</v>
@@ -12315,7 +12315,7 @@
         <v>10</v>
       </c>
       <c r="F417" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="418" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12329,13 +12329,13 @@
         <v>861</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E418" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="419" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12355,7 +12355,7 @@
         <v>10</v>
       </c>
       <c r="F419" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="420" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12369,13 +12369,13 @@
         <v>865</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E420" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="421" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12395,7 +12395,7 @@
         <v>10</v>
       </c>
       <c r="F421" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="422" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12415,7 +12415,7 @@
         <v>10</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="423" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12435,7 +12435,7 @@
         <v>10</v>
       </c>
       <c r="F423" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="424" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12449,13 +12449,13 @@
         <v>874</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E424" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="425" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12469,13 +12469,13 @@
         <v>876</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E425" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F425" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="426" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12495,7 +12495,7 @@
         <v>10</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="427" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12515,7 +12515,7 @@
         <v>10</v>
       </c>
       <c r="F427" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="428" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12529,13 +12529,13 @@
         <v>882</v>
       </c>
       <c r="D428" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E428" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F428" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E428" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F428" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="429" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12549,13 +12549,13 @@
         <v>884</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F429" s="4" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="430" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12575,7 +12575,7 @@
         <v>10</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="431" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12595,7 +12595,7 @@
         <v>10</v>
       </c>
       <c r="F431" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="432" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12609,13 +12609,13 @@
         <v>890</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E432" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="433" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12629,13 +12629,13 @@
         <v>892</v>
       </c>
       <c r="D433" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E433" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F433" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E433" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F433" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="434" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12655,7 +12655,7 @@
         <v>10</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="435" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12675,7 +12675,7 @@
         <v>10</v>
       </c>
       <c r="F435" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="436" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12689,7 +12689,7 @@
         <v>898</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E436" s="3" t="s">
         <v>10</v>
@@ -12709,13 +12709,13 @@
         <v>900</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E437" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F437" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="438" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12755,7 +12755,7 @@
         <v>10</v>
       </c>
       <c r="F439" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="440" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12769,13 +12769,13 @@
         <v>906</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E440" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="441" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12789,13 +12789,13 @@
         <v>908</v>
       </c>
       <c r="D441" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E441" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F441" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E441" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F441" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="442" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12815,7 +12815,7 @@
         <v>10</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="443" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12835,7 +12835,7 @@
         <v>10</v>
       </c>
       <c r="F443" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="444" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12849,13 +12849,13 @@
         <v>914</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E444" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="445" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12869,7 +12869,7 @@
         <v>916</v>
       </c>
       <c r="D445" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E445" s="3" t="s">
         <v>10</v>
@@ -12895,7 +12895,7 @@
         <v>10</v>
       </c>
       <c r="F446" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="447" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12915,7 +12915,7 @@
         <v>10</v>
       </c>
       <c r="F447" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="448" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12929,13 +12929,13 @@
         <v>922</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E448" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F448" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="449" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12949,13 +12949,13 @@
         <v>924</v>
       </c>
       <c r="D449" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E449" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F449" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E449" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F449" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="450" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12975,7 +12975,7 @@
         <v>10</v>
       </c>
       <c r="F450" s="2" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="451" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13009,13 +13009,13 @@
         <v>930</v>
       </c>
       <c r="D452" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E452" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F452" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E452" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F452" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="453" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13029,13 +13029,13 @@
         <v>932</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E453" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F453" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="454" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13055,7 +13055,7 @@
         <v>10</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
     </row>
     <row r="455" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13075,7 +13075,7 @@
         <v>10</v>
       </c>
       <c r="F455" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="456" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13089,13 +13089,13 @@
         <v>938</v>
       </c>
       <c r="D456" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E456" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F456" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E456" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F456" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="457" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13109,13 +13109,13 @@
         <v>940</v>
       </c>
       <c r="D457" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E457" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F457" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E457" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F457" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="458" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13135,7 +13135,7 @@
         <v>10</v>
       </c>
       <c r="F458" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="459" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13155,7 +13155,7 @@
         <v>10</v>
       </c>
       <c r="F459" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="460" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13169,13 +13169,13 @@
         <v>946</v>
       </c>
       <c r="D460" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E460" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F460" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E460" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F460" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="461" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13189,13 +13189,13 @@
         <v>948</v>
       </c>
       <c r="D461" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E461" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F461" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E461" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F461" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="462" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13235,7 +13235,7 @@
         <v>10</v>
       </c>
       <c r="F463" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="464" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13249,13 +13249,13 @@
         <v>954</v>
       </c>
       <c r="D464" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E464" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F464" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E464" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F464" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="465" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13269,13 +13269,13 @@
         <v>956</v>
       </c>
       <c r="D465" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E465" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F465" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="466" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13295,7 +13295,7 @@
         <v>10</v>
       </c>
       <c r="F466" s="2" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="467" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13315,7 +13315,7 @@
         <v>10</v>
       </c>
       <c r="F467" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="468" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13329,13 +13329,13 @@
         <v>962</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E468" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F468" s="2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="469" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13349,13 +13349,13 @@
         <v>964</v>
       </c>
       <c r="D469" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E469" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F469" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E469" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F469" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="470" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13375,7 +13375,7 @@
         <v>10</v>
       </c>
       <c r="F470" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="471" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13395,7 +13395,7 @@
         <v>10</v>
       </c>
       <c r="F471" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -13479,16 +13479,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>972</v>
@@ -13539,13 +13539,13 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>9</v>
@@ -13559,16 +13559,16 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>976</v>
@@ -13579,13 +13579,13 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>20</v>
@@ -13599,13 +13599,13 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -13619,13 +13619,13 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
@@ -13639,16 +13639,16 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>980</v>
@@ -13659,13 +13659,13 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>20</v>
@@ -13679,13 +13679,13 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
@@ -13699,13 +13699,13 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>9</v>
@@ -13719,16 +13719,16 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>984</v>
@@ -13739,13 +13739,13 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>20</v>
@@ -13759,13 +13759,13 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>9</v>
@@ -13779,13 +13779,13 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>9</v>
@@ -13799,16 +13799,16 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>988</v>
@@ -13819,13 +13819,13 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>20</v>
@@ -13839,13 +13839,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>9</v>
@@ -13859,13 +13859,13 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>9</v>
@@ -13879,16 +13879,16 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>972</v>
@@ -13899,13 +13899,13 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>20</v>
@@ -13919,13 +13919,13 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>9</v>
@@ -13939,13 +13939,13 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>9</v>
@@ -13959,16 +13959,16 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>976</v>
@@ -14048,7 +14048,7 @@
         <v>76</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>980</v>
@@ -14128,7 +14128,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>984</v>
@@ -14208,7 +14208,7 @@
         <v>92</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>988</v>
@@ -14288,7 +14288,7 @@
         <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>992</v>
@@ -14308,7 +14308,7 @@
         <v>103</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>993</v>
@@ -14368,7 +14368,7 @@
         <v>109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>996</v>
@@ -14388,7 +14388,7 @@
         <v>111</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>997</v>
@@ -14419,13 +14419,13 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>9</v>
@@ -14439,16 +14439,16 @@
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>990</v>
@@ -14459,16 +14459,16 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>991</v>
@@ -14479,13 +14479,13 @@
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>9</v>
@@ -14499,13 +14499,13 @@
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>9</v>
@@ -14519,16 +14519,16 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>994</v>
@@ -14539,16 +14539,16 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>995</v>
@@ -14559,13 +14559,13 @@
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>9</v>
@@ -14579,13 +14579,13 @@
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>9</v>
@@ -14599,16 +14599,16 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>998</v>
@@ -14619,16 +14619,16 @@
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>999</v>
@@ -14639,13 +14639,13 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>9</v>
@@ -14659,13 +14659,13 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>9</v>
@@ -14679,16 +14679,16 @@
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>992</v>
@@ -14699,16 +14699,16 @@
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>993</v>
@@ -14719,13 +14719,13 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>9</v>
@@ -14739,13 +14739,13 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>9</v>
@@ -14759,16 +14759,16 @@
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>996</v>
@@ -14779,16 +14779,16 @@
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>997</v>
@@ -14848,7 +14848,7 @@
         <v>158</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>990</v>
@@ -14868,7 +14868,7 @@
         <v>160</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>991</v>
@@ -14928,7 +14928,7 @@
         <v>166</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>994</v>
@@ -14948,7 +14948,7 @@
         <v>168</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>995</v>
@@ -15008,7 +15008,7 @@
         <v>174</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>998</v>
@@ -15028,7 +15028,7 @@
         <v>176</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>999</v>
@@ -15048,7 +15048,7 @@
         <v>179</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>1000</v>
@@ -15068,7 +15068,7 @@
         <v>181</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>1001</v>
@@ -15128,7 +15128,7 @@
         <v>187</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>1004</v>
@@ -15148,7 +15148,7 @@
         <v>189</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>1005</v>
@@ -15208,7 +15208,7 @@
         <v>195</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>1008</v>
@@ -15228,7 +15228,7 @@
         <v>197</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>1009</v>
@@ -15288,7 +15288,7 @@
         <v>203</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>1002</v>
@@ -15308,7 +15308,7 @@
         <v>205</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>1003</v>
@@ -15368,7 +15368,7 @@
         <v>211</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>1006</v>
@@ -15388,7 +15388,7 @@
         <v>213</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>1007</v>
@@ -15448,7 +15448,7 @@
         <v>219</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>1000</v>
@@ -15468,7 +15468,7 @@
         <v>221</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>1001</v>
@@ -15528,7 +15528,7 @@
         <v>227</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>1004</v>
@@ -15548,7 +15548,7 @@
         <v>229</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>1005</v>
@@ -15608,7 +15608,7 @@
         <v>235</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>1008</v>
@@ -15628,7 +15628,7 @@
         <v>237</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>1009</v>
@@ -15648,7 +15648,7 @@
         <v>240</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>1010</v>
@@ -15688,7 +15688,7 @@
         <v>244</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>1012</v>
@@ -15728,7 +15728,7 @@
         <v>248</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>1014</v>
@@ -15768,7 +15768,7 @@
         <v>252</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>1016</v>
@@ -15808,7 +15808,7 @@
         <v>256</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>1018</v>
@@ -15848,7 +15848,7 @@
         <v>260</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>1010</v>
@@ -15888,7 +15888,7 @@
         <v>264</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>1012</v>
@@ -15928,7 +15928,7 @@
         <v>268</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>1014</v>
@@ -15968,7 +15968,7 @@
         <v>272</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>1016</v>
@@ -16008,7 +16008,7 @@
         <v>276</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>1018</v>
@@ -16048,7 +16048,7 @@
         <v>280</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>1010</v>
@@ -16088,7 +16088,7 @@
         <v>284</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>1012</v>
@@ -16128,7 +16128,7 @@
         <v>288</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>1014</v>
@@ -16168,7 +16168,7 @@
         <v>292</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>1016</v>
@@ -16208,7 +16208,7 @@
         <v>296</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>1018</v>
@@ -16248,7 +16248,7 @@
         <v>300</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>1010</v>
@@ -16288,7 +16288,7 @@
         <v>304</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>1012</v>
@@ -16328,7 +16328,7 @@
         <v>308</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>1014</v>
@@ -16368,7 +16368,7 @@
         <v>312</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>1016</v>
@@ -16408,7 +16408,7 @@
         <v>316</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>1018</v>
@@ -16448,7 +16448,7 @@
         <v>320</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>1010</v>
@@ -16488,7 +16488,7 @@
         <v>324</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>1012</v>
@@ -16528,7 +16528,7 @@
         <v>328</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>1014</v>
@@ -16568,7 +16568,7 @@
         <v>332</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>1016</v>
@@ -16608,7 +16608,7 @@
         <v>336</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>1018</v>
@@ -16668,7 +16668,7 @@
         <v>343</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>1021</v>
@@ -16688,7 +16688,7 @@
         <v>345</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>1022</v>
@@ -16748,7 +16748,7 @@
         <v>351</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>1025</v>
@@ -16768,7 +16768,7 @@
         <v>353</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>1026</v>
@@ -16828,7 +16828,7 @@
         <v>359</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>1029</v>
@@ -16848,7 +16848,7 @@
         <v>361</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>1020</v>
@@ -16908,7 +16908,7 @@
         <v>367</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>1023</v>
@@ -16928,7 +16928,7 @@
         <v>369</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>1024</v>
@@ -16988,7 +16988,7 @@
         <v>375</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>1027</v>
@@ -17008,7 +17008,7 @@
         <v>377</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>1028</v>
@@ -17068,7 +17068,7 @@
         <v>383</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>1021</v>
@@ -17088,7 +17088,7 @@
         <v>385</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>1022</v>
@@ -17148,7 +17148,7 @@
         <v>391</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>1025</v>
@@ -17168,7 +17168,7 @@
         <v>393</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>1026</v>
@@ -17228,7 +17228,7 @@
         <v>399</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>1029</v>
@@ -17248,7 +17248,7 @@
         <v>401</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>1020</v>
@@ -17308,7 +17308,7 @@
         <v>407</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>1023</v>
@@ -17328,7 +17328,7 @@
         <v>409</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>1024</v>
@@ -17388,7 +17388,7 @@
         <v>415</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>1027</v>
@@ -17408,7 +17408,7 @@
         <v>417</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>1028</v>
@@ -17468,7 +17468,7 @@
         <v>423</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>1021</v>
@@ -17488,7 +17488,7 @@
         <v>425</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>1022</v>
@@ -17548,7 +17548,7 @@
         <v>431</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E207" s="4" t="s">
         <v>1025</v>
@@ -17568,7 +17568,7 @@
         <v>433</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>1026</v>
@@ -17628,7 +17628,7 @@
         <v>439</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>1029</v>
@@ -17688,7 +17688,7 @@
         <v>446</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>1032</v>
@@ -17708,7 +17708,7 @@
         <v>448</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E215" s="4" t="s">
         <v>1033</v>
@@ -17768,7 +17768,7 @@
         <v>454</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>1036</v>
@@ -17788,7 +17788,7 @@
         <v>456</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E219" s="4" t="s">
         <v>1037</v>
@@ -17848,7 +17848,7 @@
         <v>462</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>1030</v>
@@ -17868,7 +17868,7 @@
         <v>464</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>1031</v>
@@ -17928,7 +17928,7 @@
         <v>470</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>1034</v>
@@ -17948,7 +17948,7 @@
         <v>472</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>1035</v>
@@ -18008,7 +18008,7 @@
         <v>478</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>1038</v>
@@ -18028,7 +18028,7 @@
         <v>480</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>1039</v>
@@ -18088,7 +18088,7 @@
         <v>486</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>1032</v>
@@ -18108,7 +18108,7 @@
         <v>488</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>1033</v>
@@ -18168,7 +18168,7 @@
         <v>494</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>1036</v>
@@ -18188,7 +18188,7 @@
         <v>496</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E239" s="4" t="s">
         <v>1037</v>
@@ -18248,7 +18248,7 @@
         <v>502</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>1030</v>
@@ -18268,7 +18268,7 @@
         <v>504</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E243" s="4" t="s">
         <v>1031</v>
@@ -18328,7 +18328,7 @@
         <v>510</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>1034</v>
@@ -18348,7 +18348,7 @@
         <v>512</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E247" s="4" t="s">
         <v>1035</v>
@@ -18408,7 +18408,7 @@
         <v>518</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>1038</v>
@@ -18428,7 +18428,7 @@
         <v>520</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E251" s="4" t="s">
         <v>1039</v>
@@ -18488,7 +18488,7 @@
         <v>526</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>1032</v>
@@ -18508,7 +18508,7 @@
         <v>528</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E255" s="4" t="s">
         <v>1033</v>
@@ -18568,7 +18568,7 @@
         <v>534</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>1036</v>
@@ -18588,7 +18588,7 @@
         <v>536</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E259" s="4" t="s">
         <v>1037</v>
@@ -18668,7 +18668,7 @@
         <v>545</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E263" s="4" t="s">
         <v>1041</v>
@@ -18688,7 +18688,7 @@
         <v>547</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>1042</v>
@@ -18748,7 +18748,7 @@
         <v>553</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E267" s="4" t="s">
         <v>1045</v>
@@ -18768,7 +18768,7 @@
         <v>555</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>1046</v>
@@ -18828,7 +18828,7 @@
         <v>561</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E271" s="4" t="s">
         <v>1049</v>
@@ -18848,7 +18848,7 @@
         <v>563</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>1040</v>
@@ -18908,7 +18908,7 @@
         <v>569</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E275" s="4" t="s">
         <v>1043</v>
@@ -18928,7 +18928,7 @@
         <v>571</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>1044</v>
@@ -18988,7 +18988,7 @@
         <v>577</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E279" s="4" t="s">
         <v>1047</v>
@@ -19008,7 +19008,7 @@
         <v>579</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>1048</v>
@@ -19068,7 +19068,7 @@
         <v>585</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E283" s="4" t="s">
         <v>1041</v>
@@ -19088,7 +19088,7 @@
         <v>587</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>1042</v>
@@ -19148,7 +19148,7 @@
         <v>593</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E287" s="4" t="s">
         <v>1045</v>
@@ -19168,7 +19168,7 @@
         <v>595</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>1046</v>
@@ -19228,7 +19228,7 @@
         <v>601</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E291" s="4" t="s">
         <v>1049</v>
@@ -19248,7 +19248,7 @@
         <v>603</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>1040</v>
@@ -19308,7 +19308,7 @@
         <v>609</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E295" s="4" t="s">
         <v>1043</v>
@@ -19328,7 +19328,7 @@
         <v>611</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>1044</v>
@@ -19388,7 +19388,7 @@
         <v>617</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E299" s="4" t="s">
         <v>1047</v>
@@ -19408,7 +19408,7 @@
         <v>619</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>1048</v>
@@ -19448,7 +19448,7 @@
         <v>624</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>1050</v>
@@ -19468,7 +19468,7 @@
         <v>626</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E303" s="4" t="s">
         <v>1051</v>
@@ -19528,7 +19528,7 @@
         <v>632</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>1054</v>
@@ -19548,7 +19548,7 @@
         <v>634</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E307" s="4" t="s">
         <v>1055</v>
@@ -19608,7 +19608,7 @@
         <v>640</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>1058</v>
@@ -19628,7 +19628,7 @@
         <v>642</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E311" s="4" t="s">
         <v>1059</v>
@@ -19688,7 +19688,7 @@
         <v>648</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>1052</v>
@@ -19708,7 +19708,7 @@
         <v>650</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E315" s="4" t="s">
         <v>1053</v>
@@ -19768,7 +19768,7 @@
         <v>656</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>1056</v>
@@ -19788,7 +19788,7 @@
         <v>658</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E319" s="4" t="s">
         <v>1057</v>
@@ -19888,7 +19888,7 @@
         <v>669</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>1062</v>
@@ -19908,7 +19908,7 @@
         <v>671</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E325" s="4" t="s">
         <v>1063</v>
@@ -19968,7 +19968,7 @@
         <v>677</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>1066</v>
@@ -19988,7 +19988,7 @@
         <v>679</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E329" s="4" t="s">
         <v>1067</v>
@@ -20048,7 +20048,7 @@
         <v>685</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>1060</v>
@@ -20068,7 +20068,7 @@
         <v>687</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E333" s="4" t="s">
         <v>1061</v>
@@ -20128,7 +20128,7 @@
         <v>693</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>1064</v>
@@ -20148,7 +20148,7 @@
         <v>695</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E337" s="4" t="s">
         <v>1065</v>
@@ -20208,7 +20208,7 @@
         <v>701</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>1068</v>
@@ -20228,7 +20228,7 @@
         <v>703</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E341" s="4" t="s">
         <v>1069</v>
@@ -20248,7 +20248,7 @@
         <v>706</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>1070</v>
@@ -20268,7 +20268,7 @@
         <v>708</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E343" s="4" t="s">
         <v>1071</v>
@@ -20328,7 +20328,7 @@
         <v>714</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>1074</v>
@@ -20348,7 +20348,7 @@
         <v>716</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E347" s="4" t="s">
         <v>1075</v>
@@ -20408,7 +20408,7 @@
         <v>722</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>1078</v>
@@ -20428,7 +20428,7 @@
         <v>724</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E351" s="4" t="s">
         <v>1079</v>
@@ -20488,7 +20488,7 @@
         <v>730</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>1072</v>
@@ -20508,7 +20508,7 @@
         <v>732</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E355" s="4" t="s">
         <v>1073</v>
@@ -20568,7 +20568,7 @@
         <v>738</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>1076</v>
@@ -20588,7 +20588,7 @@
         <v>740</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E359" s="4" t="s">
         <v>1077</v>
@@ -20668,7 +20668,7 @@
         <v>749</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E363" s="4" t="s">
         <v>1081</v>
@@ -20708,7 +20708,7 @@
         <v>753</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E365" s="4" t="s">
         <v>1083</v>
@@ -20748,7 +20748,7 @@
         <v>757</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E367" s="4" t="s">
         <v>1085</v>
@@ -20788,7 +20788,7 @@
         <v>761</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E369" s="4" t="s">
         <v>1087</v>
@@ -20828,7 +20828,7 @@
         <v>765</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E371" s="4" t="s">
         <v>1089</v>
@@ -20868,7 +20868,7 @@
         <v>769</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E373" s="4" t="s">
         <v>1081</v>
@@ -20908,7 +20908,7 @@
         <v>773</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E375" s="4" t="s">
         <v>1083</v>
@@ -20948,7 +20948,7 @@
         <v>777</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E377" s="4" t="s">
         <v>1085</v>
@@ -20988,7 +20988,7 @@
         <v>781</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E379" s="4" t="s">
         <v>1087</v>
@@ -21028,7 +21028,7 @@
         <v>785</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E381" s="4" t="s">
         <v>1089</v>
@@ -21048,7 +21048,7 @@
         <v>788</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>1090</v>
@@ -21088,7 +21088,7 @@
         <v>792</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>1092</v>
@@ -21128,7 +21128,7 @@
         <v>796</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>1094</v>
@@ -21168,7 +21168,7 @@
         <v>800</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>1096</v>
@@ -21208,7 +21208,7 @@
         <v>804</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>1098</v>
@@ -21248,7 +21248,7 @@
         <v>808</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>1090</v>
@@ -21288,7 +21288,7 @@
         <v>812</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>1092</v>
@@ -21328,7 +21328,7 @@
         <v>816</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>1094</v>
@@ -21368,7 +21368,7 @@
         <v>820</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>1096</v>
@@ -21408,7 +21408,7 @@
         <v>824</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>1098</v>
@@ -21448,7 +21448,7 @@
         <v>829</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>1100</v>
@@ -21488,7 +21488,7 @@
         <v>833</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>1102</v>
@@ -21528,7 +21528,7 @@
         <v>837</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>1104</v>
@@ -21568,7 +21568,7 @@
         <v>841</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>1106</v>
@@ -21608,7 +21608,7 @@
         <v>845</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>1108</v>
@@ -21648,7 +21648,7 @@
         <v>849</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>1100</v>
@@ -21688,7 +21688,7 @@
         <v>853</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>1102</v>
@@ -21728,7 +21728,7 @@
         <v>857</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>1104</v>
@@ -21768,7 +21768,7 @@
         <v>861</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>1106</v>
@@ -21808,7 +21808,7 @@
         <v>865</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>1108</v>
@@ -21888,7 +21888,7 @@
         <v>874</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>1112</v>
@@ -21908,7 +21908,7 @@
         <v>876</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E425" s="4" t="s">
         <v>1113</v>
@@ -21968,7 +21968,7 @@
         <v>882</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>1116</v>
@@ -21988,7 +21988,7 @@
         <v>884</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E429" s="4" t="s">
         <v>1117</v>
@@ -22048,7 +22048,7 @@
         <v>890</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>1110</v>
@@ -22068,7 +22068,7 @@
         <v>892</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E433" s="4" t="s">
         <v>1111</v>
@@ -22128,7 +22128,7 @@
         <v>898</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>1114</v>
@@ -22148,7 +22148,7 @@
         <v>900</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E437" s="4" t="s">
         <v>1115</v>
@@ -22208,7 +22208,7 @@
         <v>906</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>1118</v>
@@ -22228,7 +22228,7 @@
         <v>908</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E441" s="4" t="s">
         <v>1119</v>
@@ -22288,7 +22288,7 @@
         <v>914</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>1112</v>
@@ -22308,7 +22308,7 @@
         <v>916</v>
       </c>
       <c r="D445" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E445" s="4" t="s">
         <v>1113</v>
@@ -22368,7 +22368,7 @@
         <v>922</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>1116</v>
@@ -22388,7 +22388,7 @@
         <v>924</v>
       </c>
       <c r="D449" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E449" s="4" t="s">
         <v>1117</v>
@@ -22448,7 +22448,7 @@
         <v>930</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>1110</v>
@@ -22468,7 +22468,7 @@
         <v>932</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E453" s="4" t="s">
         <v>1111</v>
@@ -22528,7 +22528,7 @@
         <v>938</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>1114</v>
@@ -22548,7 +22548,7 @@
         <v>940</v>
       </c>
       <c r="D457" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E457" s="4" t="s">
         <v>1115</v>
@@ -22608,7 +22608,7 @@
         <v>946</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>1118</v>
@@ -22628,7 +22628,7 @@
         <v>948</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E461" s="4" t="s">
         <v>1119</v>
@@ -22688,7 +22688,7 @@
         <v>954</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>1112</v>
@@ -22708,7 +22708,7 @@
         <v>956</v>
       </c>
       <c r="D465" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E465" s="4" t="s">
         <v>1113</v>
@@ -22768,7 +22768,7 @@
         <v>962</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>1116</v>
@@ -22788,7 +22788,7 @@
         <v>964</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E469" s="4" t="s">
         <v>1117</v>
